--- a/VerveStacks_MEX_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_MEX_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_MEX_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{16F0B8A6-0BFD-4242-8C96-483F076AF576}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FAD2EF8A-5C05-40F1-88DB-7ED5DE38FEE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{C486F204-3136-4535-8A39-07ABEF7C32B1}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{A544B948-C9D3-4E81-8FA8-90BA807ACD21}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2422,7 +2422,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FFCBB40-831D-49B7-8E08-74DFF2E758B5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10C5E3B8-4BF8-493B-9F6F-355E58FA1A8D}">
   <dimension ref="B3:L292"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_MEX_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_MEX_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_MEX_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FAD2EF8A-5C05-40F1-88DB-7ED5DE38FEE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3206ACE1-0917-4E7A-A824-A9393E1B2968}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{A544B948-C9D3-4E81-8FA8-90BA807ACD21}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{14412C05-B53F-45CC-9FC5-D05DAF6B37DA}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2422,7 +2422,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10C5E3B8-4BF8-493B-9F6F-355E58FA1A8D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C866B01A-86A8-4522-A3B5-C0E11BB9F1D6}">
   <dimension ref="B3:L292"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
